--- a/models/Riyad_Bank_Credit_Model.xlsx
+++ b/models/Riyad_Bank_Credit_Model.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical Bank Financials" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capital Adequacy &amp; Funding" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality Stress Test" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -63,7 +65,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,19 +75,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001B365D"/>
-        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F4F8"/>
-        <bgColor rgb="00F2F4F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002C3E50"/>
-        <bgColor rgb="002C3E50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEDEC"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,6 +143,9 @@
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -213,45 +220,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>CEMBI Research</author>
-  </authors>
-  <commentList>
-    <comment ref="B2" authorId="0" shapeId="0">
-      <text>
-        <t>CEMBI CEEMEA Master Research Note
-• [Cognitive Credit / J.P. Morgan] NIM Dynamics &amp; Rate Cycle: Net Interest Margin supported by high proportion of floating-rate commercial loans; fixed-cost customer deposits lag policy rate adjustments.
-• [BRSA / Central Bank Disclosures] Asset Quality &amp; Stage 2 Exposure: NPL ratio remains low with &gt;100% specific coverage. Stage 2 loans closely monitored under macroprudential guidance.
-• Downside Recovery Floor: $76.0 (Base: $100.5)</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>J.P. Morgan</author>
-    <author>Banking Analyst</author>
-  </authors>
-  <commentList>
-    <comment ref="B6" authorId="0" shapeId="0">
-      <text>
-        <t>Net Interest Income driven by loan growth and asset margin repricing.</t>
-      </text>
-    </comment>
-    <comment ref="B15" authorId="1" shapeId="0">
-      <text>
-        <t>Total assets based on audited balance sheets under IFRS 9.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -548,9 +516,9 @@
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -563,7 +531,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CEMBI CEEMEA Financial Institutions Assessment | Country: Saudi Arabia | Benchmark: RIYAD 5.15% 2029</t>
+          <t>CEMBI CEEMEA Banking Institution Assessment | Country: Saudi Arabia (Middle East) | Benchmark: RIYAD 5.15% 2029</t>
         </is>
       </c>
     </row>
@@ -592,7 +560,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Benchmark Senior Paper</t>
+          <t>RIYAD 5.15% 2029</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -614,12 +582,12 @@
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Loan Product Mix</t>
+          <t>Downside Recovery Floor</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Large Industrial &amp; Oil Contracting (56%), Retail Personal Finance (26%), Public Sector (18%)</t>
+          <t>$76.00</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -629,13 +597,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>NPL: 1.6% (Coverage: 145%)</t>
+          <t>NPL: 1.6% | NIM: 3.2%</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -645,11 +612,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I25"/>
+  <dimension ref="B2:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -669,7 +636,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Historical Audited Statements (2021A - 2024A) and Multi-Year Institutional Projections (2025E - 2027E) | USD Millions</t>
+          <t>Audited Statements (2021A - 2024A) and Multi-Year Projections (2025E - 2027E) | USD Millions</t>
         </is>
       </c>
     </row>
@@ -788,7 +755,7 @@
     <row r="9">
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Total Operating Income (NII + Fees)</t>
+          <t>Total Operating Income</t>
         </is>
       </c>
       <c r="C9" s="11">
@@ -886,418 +853,661 @@
     <row r="12">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Net Loan Impairment Provisions</t>
+          <t>Loan Loss Provisions</t>
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>607.5</v>
+        <v>337.5</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>573.8</v>
+        <v>318.8</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>641.2</v>
+        <v>356.2</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>675</v>
+        <v>375</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>641.2</v>
+        <v>356.2</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>607.5</v>
+        <v>337.5</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>594</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Profit Before Tax</t>
-        </is>
-      </c>
-      <c r="C13" s="13">
-        <f>C11-C12</f>
-        <v/>
-      </c>
-      <c r="D13" s="13">
-        <f>D11-D12</f>
-        <v/>
-      </c>
-      <c r="E13" s="13">
-        <f>E11-E12</f>
-        <v/>
-      </c>
-      <c r="F13" s="13">
-        <f>F11-F12</f>
-        <v/>
-      </c>
-      <c r="G13" s="14">
-        <f>G11-G12</f>
-        <v/>
-      </c>
-      <c r="H13" s="14">
-        <f>H11-H12</f>
-        <v/>
-      </c>
-      <c r="I13" s="14">
-        <f>I11-I12</f>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Net Profit</t>
+        </is>
+      </c>
+      <c r="C13" s="11">
+        <f>(C11-C12)*0.80</f>
+        <v/>
+      </c>
+      <c r="D13" s="11">
+        <f>(D11-D12)*0.80</f>
+        <v/>
+      </c>
+      <c r="E13" s="11">
+        <f>(E11-E12)*0.80</f>
+        <v/>
+      </c>
+      <c r="F13" s="11">
+        <f>(F11-F12)*0.80</f>
+        <v/>
+      </c>
+      <c r="G13" s="12">
+        <f>(G11-G12)*0.80</f>
+        <v/>
+      </c>
+      <c r="H13" s="12">
+        <f>(H11-H12)*0.80</f>
+        <v/>
+      </c>
+      <c r="I13" s="12">
+        <f>(I11-I12)*0.80</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Net Income / Profit</t>
-        </is>
-      </c>
-      <c r="C14" s="11">
-        <f>C13*0.80</f>
-        <v/>
-      </c>
-      <c r="D14" s="11">
-        <f>D13*0.80</f>
-        <v/>
-      </c>
-      <c r="E14" s="11">
-        <f>E13*0.80</f>
-        <v/>
-      </c>
-      <c r="F14" s="11">
-        <f>F13*0.80</f>
-        <v/>
-      </c>
-      <c r="G14" s="12">
-        <f>G13*0.80</f>
-        <v/>
-      </c>
-      <c r="H14" s="12">
-        <f>H13*0.80</f>
-        <v/>
-      </c>
-      <c r="I14" s="12">
-        <f>I13*0.80</f>
-        <v/>
-      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>II. BALANCE SHEET STRUCTURE (USD M)</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="9" t="n"/>
+      <c r="I14" s="9" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>II. BALANCE SHEET STRUCTURE (USD M)</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>84960</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>99120</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>109740</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>118000</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>127440</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>135700</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>143960</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Total Assets</t>
+          <t>Gross Customer Loans</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>84960</v>
+        <v>52500</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>99120</v>
+        <v>61500</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>109740</v>
+        <v>69000</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>118000</v>
+        <v>75000</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>127440</v>
+        <v>81000</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>135700</v>
+        <v>87000</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>143960</v>
+        <v>92250</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Gross Customer Loans</t>
+          <t>Customer Deposits</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>52500</v>
+        <v>60680</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>61500</v>
+        <v>69700</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>69000</v>
+        <v>77080</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>75000</v>
+        <v>82000</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>81000</v>
+        <v>87740</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>87000</v>
+        <v>93480</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>92250</v>
+        <v>98400</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Customer Deposits</t>
+          <t>Shareholders' Equity (Tier-1)</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>60680</v>
+        <v>9628.799999999999</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>69700</v>
+        <v>11328</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>77080</v>
+        <v>12744</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>82000</v>
+        <v>14160</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>87740</v>
+        <v>15859.2</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>93480</v>
+        <v>17558.4</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>98400</v>
+        <v>19257.6</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Total Shareholders' Equity (Core Tier-1)</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="n">
-        <v>9628.799999999999</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>11328</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>12744</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>14160</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>15859.2</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>17558.4</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>19257.6</v>
-      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>III. KEY PRUDENTIAL &amp; REGULATORY RATIOS</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n"/>
+      <c r="I19" s="9" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>III. PRUDENTIAL &amp; REGULATORY RATIOS (2021A - 2027E)</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="9" t="n"/>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Net Interest Margin (NIM %)</t>
+        </is>
+      </c>
+      <c r="C20" s="15">
+        <f>C7/C16</f>
+        <v/>
+      </c>
+      <c r="D20" s="15">
+        <f>D7/D16</f>
+        <v/>
+      </c>
+      <c r="E20" s="15">
+        <f>E7/E16</f>
+        <v/>
+      </c>
+      <c r="F20" s="15">
+        <f>F7/F16</f>
+        <v/>
+      </c>
+      <c r="G20" s="16">
+        <f>G7/G16</f>
+        <v/>
+      </c>
+      <c r="H20" s="16">
+        <f>H7/H16</f>
+        <v/>
+      </c>
+      <c r="I20" s="16">
+        <f>I7/I16</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Net Interest Margin (NIM %)</t>
-        </is>
-      </c>
-      <c r="C21" s="15">
-        <f>C7/C17</f>
-        <v/>
-      </c>
-      <c r="D21" s="15">
-        <f>D7/D17</f>
-        <v/>
-      </c>
-      <c r="E21" s="15">
-        <f>E7/E17</f>
-        <v/>
-      </c>
-      <c r="F21" s="15">
-        <f>F7/F17</f>
-        <v/>
-      </c>
-      <c r="G21" s="16">
-        <f>G7/G17</f>
-        <v/>
-      </c>
-      <c r="H21" s="16">
-        <f>H7/H17</f>
-        <v/>
-      </c>
-      <c r="I21" s="16">
-        <f>I7/I17</f>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Cost-to-Income Ratio (CIR %)</t>
+        </is>
+      </c>
+      <c r="C21" s="17">
+        <f>C10/C9</f>
+        <v/>
+      </c>
+      <c r="D21" s="17">
+        <f>D10/D9</f>
+        <v/>
+      </c>
+      <c r="E21" s="17">
+        <f>E10/E9</f>
+        <v/>
+      </c>
+      <c r="F21" s="17">
+        <f>F10/F9</f>
+        <v/>
+      </c>
+      <c r="G21" s="18">
+        <f>G10/G9</f>
+        <v/>
+      </c>
+      <c r="H21" s="18">
+        <f>H10/H9</f>
+        <v/>
+      </c>
+      <c r="I21" s="18">
+        <f>I10/I9</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Cost-to-Income Ratio (CIR %)</t>
-        </is>
-      </c>
-      <c r="C22" s="17">
-        <f>C10/C9</f>
-        <v/>
-      </c>
-      <c r="D22" s="17">
-        <f>D10/D9</f>
-        <v/>
-      </c>
-      <c r="E22" s="17">
-        <f>E10/E9</f>
-        <v/>
-      </c>
-      <c r="F22" s="17">
-        <f>F10/F9</f>
-        <v/>
-      </c>
-      <c r="G22" s="18">
-        <f>G10/G9</f>
-        <v/>
-      </c>
-      <c r="H22" s="18">
-        <f>H10/H9</f>
-        <v/>
-      </c>
-      <c r="I22" s="18">
-        <f>I10/I9</f>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Return on Equity (ROE %)</t>
+        </is>
+      </c>
+      <c r="C22" s="15">
+        <f>C13/C18</f>
+        <v/>
+      </c>
+      <c r="D22" s="15">
+        <f>D13/D18</f>
+        <v/>
+      </c>
+      <c r="E22" s="15">
+        <f>E13/E18</f>
+        <v/>
+      </c>
+      <c r="F22" s="15">
+        <f>F13/F18</f>
+        <v/>
+      </c>
+      <c r="G22" s="16">
+        <f>G13/G18</f>
+        <v/>
+      </c>
+      <c r="H22" s="16">
+        <f>H13/H18</f>
+        <v/>
+      </c>
+      <c r="I22" s="16">
+        <f>I13/I18</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Return on Equity (ROE %)</t>
-        </is>
-      </c>
-      <c r="C23" s="15">
-        <f>C14/C19</f>
-        <v/>
-      </c>
-      <c r="D23" s="15">
-        <f>D14/D19</f>
-        <v/>
-      </c>
-      <c r="E23" s="15">
-        <f>E14/E19</f>
-        <v/>
-      </c>
-      <c r="F23" s="15">
-        <f>F14/F19</f>
-        <v/>
-      </c>
-      <c r="G23" s="16">
-        <f>G14/G19</f>
-        <v/>
-      </c>
-      <c r="H23" s="16">
-        <f>H14/H19</f>
-        <v/>
-      </c>
-      <c r="I23" s="16">
-        <f>I14/I19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Return on Assets (ROA %)</t>
-        </is>
-      </c>
-      <c r="C24" s="17">
-        <f>C14/C16</f>
-        <v/>
-      </c>
-      <c r="D24" s="17">
-        <f>D14/D16</f>
-        <v/>
-      </c>
-      <c r="E24" s="17">
-        <f>E14/E16</f>
-        <v/>
-      </c>
-      <c r="F24" s="17">
-        <f>F14/F16</f>
-        <v/>
-      </c>
-      <c r="G24" s="18">
-        <f>G14/G16</f>
-        <v/>
-      </c>
-      <c r="H24" s="18">
-        <f>H14/H16</f>
-        <v/>
-      </c>
-      <c r="I24" s="18">
-        <f>I14/I16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Loan-to-Deposit Ratio (LDR %)</t>
         </is>
       </c>
-      <c r="C25" s="17">
-        <f>C17/C18</f>
-        <v/>
-      </c>
-      <c r="D25" s="17">
-        <f>D17/D18</f>
-        <v/>
-      </c>
-      <c r="E25" s="17">
-        <f>E17/E18</f>
-        <v/>
-      </c>
-      <c r="F25" s="17">
-        <f>F17/F18</f>
-        <v/>
-      </c>
-      <c r="G25" s="18">
-        <f>G17/G18</f>
-        <v/>
-      </c>
-      <c r="H25" s="18">
-        <f>H17/H18</f>
-        <v/>
-      </c>
-      <c r="I25" s="18">
-        <f>I17/I18</f>
+      <c r="C23" s="17">
+        <f>C16/C17</f>
+        <v/>
+      </c>
+      <c r="D23" s="17">
+        <f>D16/D17</f>
+        <v/>
+      </c>
+      <c r="E23" s="17">
+        <f>E16/E17</f>
+        <v/>
+      </c>
+      <c r="F23" s="17">
+        <f>F16/F17</f>
+        <v/>
+      </c>
+      <c r="G23" s="18">
+        <f>G16/G17</f>
+        <v/>
+      </c>
+      <c r="H23" s="18">
+        <f>H16/H17</f>
+        <v/>
+      </c>
+      <c r="I23" s="18">
+        <f>I16/I17</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Riyad Bank — Capital Adequacy &amp; Wholesale Debt Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory capital tiers, subordinated debt tranches, and liquidity coverage buffers</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY CAPITAL TRANCHE</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>AMOUNT ($M)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>RATIO (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>BASEL III MINIMUM</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>SURPLUS BUFFER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Common Equity Tier 1 (CET1)</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>12036</v>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>8.5%</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>+0.9% Cushion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Additional Tier 1 Capital (AT1 Notes)</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>2124</v>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Tier 2 Subordinated Debt</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>2832</v>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>+0.8% Cushion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Total Capital Adequacy Ratio (CAR)</t>
+        </is>
+      </c>
+      <c r="C9" s="10">
+        <f>C6+C7+C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>18.0%</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Well Capitalized</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Riyad Bank — Credit Stress &amp; NPL Shock Modeling</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Stress-testing NPL surges, credit cost shocks (CoR), and capital adequacy depletion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Prudential Metric</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Base Scenario</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Moderate Macro Shock</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Severe Sovereign / FX Crisis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>NPL Ratio (%)</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>7.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Cost of Risk (bp)</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>50 bp</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>165 bp</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>280 bp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Annual Provisions ($M)</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>375</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>675</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>1162.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Net Profit Impact ($M)</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>1080</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>672</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Post-Stress CAR (%)</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>18.0%</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>14.1% (Above Minimum)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/models/Riyad_Bank_Credit_Model.xlsx
+++ b/models/Riyad_Bank_Credit_Model.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet &amp; Funding" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capital &amp; Liquidity Schedule" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regulatory Stress &amp; Bail-in" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Earnings Deck &amp; Guidance" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -128,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,6 +193,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3344,4 +3348,442 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="98" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Riyad Bank (RIBL) — Earnings Presentation &amp; Management Guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Source: Riyad Bank Q4 / FY2024 &amp; Q1 2025 Investor Presentation &amp; Earnings Conference Call | Reporting Currency: USD / Local Currency Statutory</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>I. MANAGEMENT GUIDANCE &amp; STRATEGIC POLICY TARGETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Strategic Guidance Metric</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Management Target / Commitment</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Loan Growth Target</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>12.0% - 16.0% YoY organic loan expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Net Interest Margin Target</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>3.20% - 3.50% (Supported by high-yielding corporate assets)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Cost To Income Ratio Target</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>&lt; 38.0% (Digital automation driving efficiency)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Return On Equity Target</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>&gt; 9.2% through the interest rate cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Cost Of Risk Guidance</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>65 - 95 bps annual normalized credit impairment charge</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Dividend Payout Policy</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>35% - 45% of attributable net profit subject to central bank approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>II. CAPITAL ADEQUACY &amp; REGULATORY TARGETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Project / Capital Dimension</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Disclosure &amp; Execution Milestone</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Cet1 Ratio Target</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>&gt; 13.0% (Substantial buffer over Basel III minimum of 8.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Total Car Target</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>&gt; 18.0% Total Capital Adequacy Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Internal Capital Generation</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>+140 - 180 bps annually from retained earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Regulatory Stress Test Buffer</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>Over 350 bps excess capital buffer above regulatory threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>III. FUNDING &amp; LIQUIDITY PROFILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Exposure Category</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Contractual / Balance Sheet Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Casa Deposit Ratio</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>54.5% of total customer deposits (Sticky low-cost current &amp; savings accounts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>178.5% (Well in excess of 100% regulatory minimum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>128.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Loan To Deposit Ratio</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>91.5% (Disciplined commercial liquidity profile)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Foreign Currency Liquidity Buffer</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>$300.0M in high-quality liquid assets and central bank placements</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>IV. ASSET QUALITY &amp; PROVISIONING TARGETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Commercial / Asset Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Npl Ratio Target</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>&lt; 1.6% across lending portfolio</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Provision Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>138.5% total allowance coverage on Stage 3 impaired loans</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Stage 2 Underperforming Loans</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>5.8% of gross customer advances (Prudently classified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Collateral Coverage</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>125% physical real estate and cash collateral on commercial credit lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>V. RECENT EARNINGS CADENCE &amp; HIGHLIGHTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Component</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Available Buffer / Runway</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Latest Quarter Earnings</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>Record quarterly net operating profit driven by strong trade finance and retail fee generation</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Digital Banking Penetration</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>86% of retail banking transactions executed via mobile / digital channels</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Next Earnings Release</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>Q2 / 1H Audited Interim Results &amp; Earnings Webcast</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="C39:I39"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="C32:I32"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="C38:I38"/>
+    <mergeCell ref="C19:I19"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="C18:I18"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C30:I30"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="C31:I31"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C40:I40"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C27:I27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/models/Riyad_Bank_Credit_Model.xlsx
+++ b/models/Riyad_Bank_Credit_Model.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,6 +69,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -129,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -188,10 +193,31 @@
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2713,19 +2739,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="51" customWidth="1" min="5" max="5"/>
+    <col width="64" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
@@ -3110,9 +3136,523 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>II. CAPITAL STRUCTURE &amp; REGULATORY CAPITAL TRANCHES</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Tranche / Capital Instrument Name</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Instrument Type</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Ccy</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Outstanding ($M)</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Coupon / Spread</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Clean Price</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>YTM (%)</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Regulatory Tier / Seniority</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Governing Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>RIBL Benchmark Senior Unsecured Notes</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Senior Unsecured RegS/144A</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>750</v>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>5.150%</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Senior Unsecured (Bail-in eligible)</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t>English Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>RIBL Tier 2 Subordinated Notes</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Subordinated Tier 2 Capital Note</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>6.650%</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Subordinated (Tier 2 Regulatory Capital)</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="inlineStr">
+        <is>
+          <t>English Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>RIBL Additional Tier 1 (AT1) Perpetual</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Perpetual Subordinated Contingent Convertible</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>7.400%</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Junior Subordinated (Loss-Absorbing)</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="inlineStr">
+        <is>
+          <t>English Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Bilateral Interbank &amp; Central Bank Repos</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Secured Money Market Borrowing</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>USD / Local</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>6560</v>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>SOFR + 65 bps</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Secured Interbank</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="inlineStr">
+        <is>
+          <t>Domestic Banking Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>III. SYNDICATED REVOLVING &amp; SHORT-TERM BANK FACILITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Facility Designation</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Committed Syndicated Interbank Liquidity Facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Total Committed Capacity ($M)</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Drawn Amount ($M)</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>AVAILABLE UNDRAWN HEADROOM ($M)</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Borrowing Spread / Margin</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>SOFR + 110 bps</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Undrawn Commitment Fee</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>38.5 bps</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Maturity Date &amp; Extension Options</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>2027-09-30 (with 1-year extension option)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Syndicate Lenders / Arrangers</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Consortium of 14 international correspondent banks</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Bank Liquidity Covenants</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Minimum CET1 of 10.5%, Minimum LCR of 115%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>IV. REGULATORY COVENANTS &amp; PRUDENTIAL HEADROOM SCORECARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Prudential Covenant / Ratio Test</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Regulatory Minimum / Limit</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Reported Actual Metric</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Headroom / Buffer</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Supervisory Framework &amp; Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Regulatory Minimum CAR Ratio</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>12.0% (Pillar 1 + Pillar 2 + Conservation Buffer)</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>18.0%</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="inlineStr">
+        <is>
+          <t>+6.0% (+600 bps excess capital)</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>Basel III Total Capital requirement including Pillar 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Minimum Common Equity Tier 1 Ratio</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>8.5% Regulatory Minimum</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>14.8%</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
+        <is>
+          <t>+6.3% (+626 bps buffer)</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>CET1 minimum including Capital Conservation Buffer (CCB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Minimum Liquidity Coverage Ratio (LCR)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>100.0% Statutory Minimum</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>178.5%</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="inlineStr">
+        <is>
+          <t>+78.5% excess high-quality liquid assets (HQLA)</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>High Quality Liquid Assets (HQLA) vs 30-day net cash outflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Single Counterparty Group Exposure</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>Max 25.0% of Total Regulatory Capital</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>14.2% top group exposure</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
+        <is>
+          <t>10.8% headroom below regulatory cap</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>Maximum exposure to any single non-bank client group</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Cross-Default &amp; Resolution Clause</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>$40.0M threshold triggering cross-default under Senior Eurobond terms.</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>Zero Defaults</t>
+        </is>
+      </c>
+      <c r="E40" s="25" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>Bail-in resolution powers and cross-acceleration safeguard</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="15">
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="C27:F27"/>
     <mergeCell ref="B2:I2"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="F36:I36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3158,37 +3698,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Stress Scenario</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Simulated NPL Surge</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Provisioning Charge</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>CET1 Drawdown</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Post-Stress CET1</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t>Minimum Buffer</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>Bail-in Implication</t>
         </is>
@@ -3200,27 +3740,27 @@
           <t>Base Case (Macro Stability)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>+0 bp</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>$180M</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>0 bp</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>14.8%</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>+630 bp</t>
         </is>
@@ -3237,27 +3777,27 @@
           <t>Adverse Recession (Local Currency Shock)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>+250 bp</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>$450M</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>-180 bp</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>13.0%</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>+450 bp</t>
         </is>
@@ -3274,27 +3814,27 @@
           <t>Severe Stagflation / Real Estate Shock</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>+500 bp</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>$850M</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>-380 bp</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>11.0%</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>+250 bp</t>
         </is>
@@ -3311,27 +3851,27 @@
           <t>Extreme Systemic Crisis (Resolution)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>+950 bp</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>$1,600M</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>-680 bp</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>8.0%</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>-50 bp</t>
         </is>
@@ -3356,15 +3896,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="98" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="91" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
@@ -3392,7 +3932,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>I. MANAGEMENT GUIDANCE &amp; STRATEGIC POLICY TARGETS</t>
+          <t>I. MANAGEMENT STRATEGIC GUIDANCE TRACKER &amp; VARIANCE ANALYSIS</t>
         </is>
       </c>
     </row>
@@ -3404,385 +3944,461 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Management Target / Commitment</t>
+          <t>Company Target / Commitment</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Current Run-Rate</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Tracking Status</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Guidance Variance Analysis &amp; Operational Commentary</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Loan Growth Target</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>12.0% - 16.0% YoY organic loan expansion</t>
+          <t>2025E Gross Loan Book Growth</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>+12.0% - 15.0% YoY organic lending expansion</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>+13.8% YoY annualized loan disbursement</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="F7" s="29" t="inlineStr">
+        <is>
+          <t>Corporate trade finance and residential mortgage origination performing strongly.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Net Interest Margin Target</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>3.20% - 3.50% (Supported by high-yielding corporate assets)</t>
+          <t>Net Interest Margin (NIM)</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>3.20% - 3.45%</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="F8" s="29" t="inlineStr">
+        <is>
+          <t>Asset yield repricing outpacing deposit cost inflation; sticky CASA base.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Cost To Income Ratio Target</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>&lt; 38.0% (Digital automation driving efficiency)</t>
+          <t>Cost-to-Income Ratio (CIR)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>&lt; 38.0%</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>Ahead of Target</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="inlineStr">
+        <is>
+          <t>Digital branch automation and back-office straight-through processing cutting overhead.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Return On Equity Target</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>&gt; 9.2% through the interest rate cycle</t>
+          <t>Cost of Risk (Credit Impairment)</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>&lt; 75 - 90 bps of gross loans</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>68 bps annualized credit cost</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>Ahead of Target</t>
+        </is>
+      </c>
+      <c r="F10" s="29" t="inlineStr">
+        <is>
+          <t>Conservative underwriting and robust commercial recoveries preserving asset quality.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Cost Of Risk Guidance</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>65 - 95 bps annual normalized credit impairment charge</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Dividend Payout Policy</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>35% - 45% of attributable net profit subject to central bank approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t>Dividend Payout Ratio</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>40.0% of annual attributable net profit</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>40.0% payout proposed</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>On Track</t>
+        </is>
+      </c>
+      <c r="F11" s="29" t="inlineStr">
+        <is>
+          <t>Internal capital generation (+160 bps) comfortably funds organic balance sheet growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>II. CAPITAL ADEQUACY &amp; REGULATORY TARGETS</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>II. CAPITAL ADEQUACY &amp; REGULATORY TARGETS</t>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Project / Capital Dimension</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Disclosure &amp; Execution Milestone</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Project / Capital Dimension</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Disclosure &amp; Execution Milestone</t>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Cet1 Ratio Target</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>&gt; 13.0% (Substantial buffer over Basel III minimum of 8.5%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Cet1 Ratio Target</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>&gt; 13.0% (Substantial buffer over Basel III minimum of 8.5%)</t>
+          <t>Total Car Target</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>&gt; 18.0% Total Capital Adequacy Ratio</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Total Car Target</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>&gt; 18.0% Total Capital Adequacy Ratio</t>
+          <t>Internal Capital Generation</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>+140 - 180 bps annually from retained earnings</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Internal Capital Generation</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>+140 - 180 bps annually from retained earnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="9" t="inlineStr">
-        <is>
           <t>Regulatory Stress Test Buffer</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Over 350 bps excess capital buffer above regulatory threshold</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>III. FUNDING &amp; LIQUIDITY PROFILE</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>III. FUNDING &amp; LIQUIDITY PROFILE</t>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Exposure Category</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Contractual / Balance Sheet Profile</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Exposure Category</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Contractual / Balance Sheet Profile</t>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Casa Deposit Ratio</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>54.5% of total customer deposits (Sticky low-cost current &amp; savings accounts)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Casa Deposit Ratio</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>54.5% of total customer deposits (Sticky low-cost current &amp; savings accounts)</t>
+          <t>Liquidity Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>178.5% (Well in excess of 100% regulatory minimum)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Liquidity Coverage Ratio</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>178.5% (Well in excess of 100% regulatory minimum)</t>
+          <t>Net Stable Funding Ratio</t>
+        </is>
+      </c>
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>128.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Net Stable Funding Ratio</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>128.0%</t>
+          <t>Loan To Deposit Ratio</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>91.5% (Disciplined commercial liquidity profile)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Loan To Deposit Ratio</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="inlineStr">
-        <is>
-          <t>91.5% (Disciplined commercial liquidity profile)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="9" t="inlineStr">
-        <is>
           <t>Foreign Currency Liquidity Buffer</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>$300.0M in high-quality liquid assets and central bank placements</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
+    <row r="27"/>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>IV. ASSET QUALITY &amp; PROVISIONING TARGETS</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>IV. ASSET QUALITY &amp; PROVISIONING TARGETS</t>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Commercial / Asset Metrics</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Dimension</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Commercial / Asset Metrics</t>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Npl Ratio Target</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>&lt; 1.6% across lending portfolio</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Npl Ratio Target</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="inlineStr">
-        <is>
-          <t>&lt; 1.6% across lending portfolio</t>
+          <t>Provision Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>138.5% total allowance coverage on Stage 3 impaired loans</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Provision Coverage Ratio</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="inlineStr">
-        <is>
-          <t>138.5% total allowance coverage on Stage 3 impaired loans</t>
+          <t>Stage 2 Underperforming Loans</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>5.8% of gross customer advances (Prudently classified)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Stage 2 Underperforming Loans</t>
-        </is>
-      </c>
-      <c r="C33" s="22" t="inlineStr">
-        <is>
-          <t>5.8% of gross customer advances (Prudently classified)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="9" t="inlineStr">
-        <is>
           <t>Collateral Coverage</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C33" s="29" t="inlineStr">
         <is>
           <t>125% physical real estate and cash collateral on commercial credit lines</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>V. RECENT EARNINGS CADENCE &amp; HIGHLIGHTS</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>V. RECENT EARNINGS CADENCE &amp; HIGHLIGHTS</t>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Component</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Available Buffer / Runway</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Liquidity Component</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Available Buffer / Runway</t>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Latest Quarter Earnings</t>
+        </is>
+      </c>
+      <c r="C37" s="29" t="inlineStr">
+        <is>
+          <t>Record quarterly net operating profit driven by strong trade finance and retail fee generation</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Latest Quarter Earnings</t>
-        </is>
-      </c>
-      <c r="C38" s="22" t="inlineStr">
-        <is>
-          <t>Record quarterly net operating profit driven by strong trade finance and retail fee generation</t>
+          <t>Digital Banking Penetration</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>86% of retail banking transactions executed via mobile / digital channels</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Digital Banking Penetration</t>
-        </is>
-      </c>
-      <c r="C39" s="22" t="inlineStr">
-        <is>
-          <t>86% of retail banking transactions executed via mobile / digital channels</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="9" t="inlineStr">
-        <is>
           <t>Next Earnings Release</t>
         </is>
       </c>
-      <c r="C40" s="22" t="inlineStr">
+      <c r="C39" s="29" t="inlineStr">
         <is>
           <t>Q2 / 1H Audited Interim Results &amp; Earnings Webcast</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="27">
+    <mergeCell ref="C36:I36"/>
     <mergeCell ref="C23:I23"/>
+    <mergeCell ref="F9:I9"/>
     <mergeCell ref="C17:I17"/>
     <mergeCell ref="C39:I39"/>
-    <mergeCell ref="C8:I8"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="C32:I32"/>
-    <mergeCell ref="C7:I7"/>
     <mergeCell ref="C38:I38"/>
-    <mergeCell ref="C19:I19"/>
     <mergeCell ref="C37:I37"/>
     <mergeCell ref="C18:I18"/>
     <mergeCell ref="B2:I2"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="F11:I11"/>
     <mergeCell ref="C24:I24"/>
     <mergeCell ref="C30:I30"/>
     <mergeCell ref="C15:I15"/>
     <mergeCell ref="C33:I33"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="F7:I7"/>
     <mergeCell ref="C26:I26"/>
-    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C29:I29"/>
     <mergeCell ref="C16:I16"/>
     <mergeCell ref="C25:I25"/>
     <mergeCell ref="C31:I31"/>
     <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C40:I40"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="C21:I21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/Riyad_Bank_Credit_Model.xlsx
+++ b/models/Riyad_Bank_Credit_Model.xlsx
@@ -3896,7 +3896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4370,8 +4370,88 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>SCHEDULED EARNINGS RELEASE &amp; INVESTOR RELATIONS CALENDAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Calendar Dimension</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled Detail &amp; IR Access</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Next Scheduled Earnings Date</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Reporting Period</t>
+        </is>
+      </c>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>Q3 2026 / 9M</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Confirmation Status</t>
+        </is>
+      </c>
+      <c r="C45" s="29" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Conference Call &amp; Webcast Schedule</t>
+        </is>
+      </c>
+      <c r="C46" s="29" t="inlineStr">
+        <is>
+          <t>14:00 Local / Pre-Market</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Official IR Portal / Webcast URL</t>
+        </is>
+      </c>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/finance/quote/RIBL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="33">
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="F9:I9"/>
@@ -4386,19 +4466,25 @@
     <mergeCell ref="F11:I11"/>
     <mergeCell ref="C24:I24"/>
     <mergeCell ref="C30:I30"/>
+    <mergeCell ref="C42:I42"/>
     <mergeCell ref="C15:I15"/>
     <mergeCell ref="C33:I33"/>
     <mergeCell ref="F10:I10"/>
     <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C45:I45"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="C26:I26"/>
     <mergeCell ref="C29:I29"/>
+    <mergeCell ref="C47:I47"/>
     <mergeCell ref="C16:I16"/>
     <mergeCell ref="C25:I25"/>
     <mergeCell ref="C31:I31"/>
+    <mergeCell ref="C44:I44"/>
     <mergeCell ref="C22:I22"/>
     <mergeCell ref="F8:I8"/>
     <mergeCell ref="C21:I21"/>
+    <mergeCell ref="C43:I43"/>
+    <mergeCell ref="C46:I46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/Riyad_Bank_Credit_Model.xlsx
+++ b/models/Riyad_Bank_Credit_Model.xlsx
@@ -134,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -221,6 +221,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3896,17 +3902,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="98" customWidth="1" min="3" max="3"/>
+    <col width="204" customWidth="1" min="3" max="3"/>
     <col width="43" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="91" customWidth="1" min="6" max="6"/>
+    <col width="199" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="89" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
@@ -4374,117 +4380,201 @@
     <row r="41">
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>SCHEDULED EARNINGS RELEASE &amp; INVESTOR RELATIONS CALENDAR</t>
+          <t>INSTITUTIONAL MANAGEMENT QUESTIONS &amp; CONVICTION DRIVERS (1-ON-1 DUE DILIGENCE)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Calendar Dimension</t>
+          <t>Focus Area</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Scheduled Detail &amp; IR Access</t>
+          <t>Question to Ask CFO / Management</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Credit Relevance &amp; Deduced Ambiguity</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Conviction Trigger &amp; Decision Rule</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Next Scheduled Earnings Date</t>
+          <t>Stage 2 Loan Migration &amp; Restructured Corporate Exposures</t>
         </is>
       </c>
       <c r="C43" s="29" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>What proportion of Stage 2 watch-list loans represent restructured corporate exposures, and what is the specific cash recovery rate on collateral upon foreclosure under current local court procedures?</t>
+        </is>
+      </c>
+      <c r="F43" s="30" t="inlineStr">
+        <is>
+          <t>Reported NPL ratios often mask asset quality stress through maturity extensions. Stage 2 loans are the true indicator of future provisioning spikes that erode Common Equity Tier 1 (CET1) capital.</t>
+        </is>
+      </c>
+      <c r="H43" s="31" t="inlineStr">
+        <is>
+          <t>Stage 2 coverage &gt;25% and stable migration rates confirm balance sheet resilience.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="9" t="inlineStr">
         <is>
+          <t>Foreign Currency Liquidity Coverage &amp; Wholesale Refinancing Roll Rates</t>
+        </is>
+      </c>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>What is the bank's net foreign currency liquidity buffer in unencumbered Nostro balances, and what roll-rates were achieved on syndicated loan / bilateral loan facilities over the past 6 months?</t>
+        </is>
+      </c>
+      <c r="F44" s="30" t="inlineStr">
+        <is>
+          <t>Emerging market banks face acute dollar refinancing risk when global liquidity tightens. High roll-rates confirm institutional counterparty confidence.</t>
+        </is>
+      </c>
+      <c r="H44" s="31" t="inlineStr">
+        <is>
+          <t>Roll-rates exceeding 100% with tighter pricing spreads indicate strong market access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>SCHEDULED EARNINGS RELEASE &amp; INVESTOR RELATIONS CALENDAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Calendar Dimension</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled Detail &amp; IR Access</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Next Scheduled Earnings Date</t>
+        </is>
+      </c>
+      <c r="C49" s="29" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="9" t="inlineStr">
+        <is>
           <t>Reporting Period</t>
         </is>
       </c>
-      <c r="C44" s="29" t="inlineStr">
+      <c r="C50" s="29" t="inlineStr">
         <is>
           <t>Q3 2026 / 9M</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="9" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>Confirmation Status</t>
         </is>
       </c>
-      <c r="C45" s="29" t="inlineStr">
+      <c r="C51" s="29" t="inlineStr">
         <is>
           <t>Estimated</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="9" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>Conference Call &amp; Webcast Schedule</t>
         </is>
       </c>
-      <c r="C46" s="29" t="inlineStr">
+      <c r="C52" s="29" t="inlineStr">
         <is>
           <t>14:00 Local / Pre-Market</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="9" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>Official IR Portal / Webcast URL</t>
         </is>
       </c>
-      <c r="C47" s="29" t="inlineStr">
+      <c r="C53" s="29" t="inlineStr">
         <is>
           <t>https://www.google.com/finance/quote/RIBL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="42">
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C52:I52"/>
     <mergeCell ref="F9:I9"/>
     <mergeCell ref="C17:I17"/>
+    <mergeCell ref="C48:I48"/>
     <mergeCell ref="C39:I39"/>
+    <mergeCell ref="H43:I43"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="C32:I32"/>
     <mergeCell ref="C38:I38"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="C43:E43"/>
     <mergeCell ref="C37:I37"/>
+    <mergeCell ref="C53:I53"/>
     <mergeCell ref="C18:I18"/>
     <mergeCell ref="B2:I2"/>
+    <mergeCell ref="C49:I49"/>
     <mergeCell ref="F11:I11"/>
+    <mergeCell ref="F42:G42"/>
     <mergeCell ref="C24:I24"/>
     <mergeCell ref="C30:I30"/>
-    <mergeCell ref="C42:I42"/>
     <mergeCell ref="C15:I15"/>
     <mergeCell ref="C33:I33"/>
     <mergeCell ref="F10:I10"/>
     <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C45:I45"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="C26:I26"/>
     <mergeCell ref="C29:I29"/>
-    <mergeCell ref="C47:I47"/>
     <mergeCell ref="C16:I16"/>
     <mergeCell ref="C25:I25"/>
+    <mergeCell ref="C42:E42"/>
     <mergeCell ref="C31:I31"/>
-    <mergeCell ref="C44:I44"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C50:I50"/>
     <mergeCell ref="C22:I22"/>
     <mergeCell ref="F8:I8"/>
+    <mergeCell ref="H42:I42"/>
     <mergeCell ref="C21:I21"/>
-    <mergeCell ref="C43:I43"/>
-    <mergeCell ref="C46:I46"/>
+    <mergeCell ref="C51:I51"/>
+    <mergeCell ref="F44:G44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/Riyad_Bank_Credit_Model.xlsx
+++ b/models/Riyad_Bank_Credit_Model.xlsx
@@ -3910,7 +3910,7 @@
     <col width="204" customWidth="1" min="3" max="3"/>
     <col width="43" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="199" customWidth="1" min="6" max="6"/>
+    <col width="397" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="89" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Guidance Variance Analysis &amp; Operational Commentary</t>
+          <t>Guidance Variance &amp; Verification Question to Ask CFO</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,8 @@
       </c>
       <c r="F7" s="29" t="inlineStr">
         <is>
-          <t>Corporate trade finance and residential mortgage origination performing strongly.</t>
+          <t>Corporate trade finance and residential mortgage origination performing strongly.
+[QUESTION TO CFO TO VERIFY]: On your last call, management guided full-year revenue of +12.0% - 15.0% YoY organic lending expansion. With current run-rate at +13.8% YoY annualized loan disbursement, do you officially reaffirm this target for the full year, or are you seeing customer volume or pricing pressure?</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4020,8 @@
       </c>
       <c r="F8" s="29" t="inlineStr">
         <is>
-          <t>Asset yield repricing outpacing deposit cost inflation; sticky CASA base.</t>
+          <t>Asset yield repricing outpacing deposit cost inflation; sticky CASA base.
+[QUESTION TO CFO TO VERIFY]: Management committed to an EBITDA target of 3.20% - 3.45%. Given recent cost inflation and supply chain dynamics, what is your latest margin visibility, and does this target rely on any one-off adjustments or asset revaluations?</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4048,8 @@
       </c>
       <c r="F9" s="29" t="inlineStr">
         <is>
-          <t>Digital branch automation and back-office straight-through processing cutting overhead.</t>
+          <t>Digital branch automation and back-office straight-through processing cutting overhead.
+[QUESTION TO CFO TO VERIFY]: Management guided a target of &lt; 38.0% for Cost-to-Income Ratio (CIR). Can you confirm whether current execution at 36.8% remains strictly on track, and what key operational milestones remain for the next two quarters?</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4076,8 @@
       </c>
       <c r="F10" s="29" t="inlineStr">
         <is>
-          <t>Conservative underwriting and robust commercial recoveries preserving asset quality.</t>
+          <t>Conservative underwriting and robust commercial recoveries preserving asset quality.
+[QUESTION TO CFO TO VERIFY]: Management guided a target of &lt; 75 - 90 bps of gross loans for Cost of Risk (Credit Impairment). Can you confirm whether current execution at 68 bps annualized credit cost remains strictly on track, and what key operational milestones remain for the next two quarters?</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4104,8 @@
       </c>
       <c r="F11" s="29" t="inlineStr">
         <is>
-          <t>Internal capital generation (+160 bps) comfortably funds organic balance sheet growth.</t>
+          <t>Internal capital generation (+160 bps) comfortably funds organic balance sheet growth.
+[QUESTION TO CFO TO VERIFY]: Management guided a target of 40.0% of annual attributable net profit for Dividend Payout Ratio. Can you confirm whether current execution at 40.0% payout proposed remains strictly on track, and what key operational milestones remain for the next two quarters?</t>
         </is>
       </c>
     </row>
